--- a/Lumerical/materials.xlsx
+++ b/Lumerical/materials.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\clapc\OneDrive\Desktop\Postdoc\PostdocResearch\SFU researches\__PhotonicsPDK__Oh\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\clapc\OneDrive\Desktop\Postdoc\PostdocResearch\SFUresearches\photonics_pdk_oh\Lumerical\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DC0E5715-EEC0-4AE3-A87A-F8BC70E7C829}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{97E8F44A-B14E-4A47-9E9B-22BCAFCA3FCE}"/>
+    <workbookView xWindow="-17610" yWindow="285" windowWidth="17535" windowHeight="6990" xr2:uid="{97E8F44A-B14E-4A47-9E9B-22BCAFCA3FCE}"/>
   </bookViews>
   <sheets>
     <sheet name="materials" sheetId="1" r:id="rId1"/>
